--- a/chl-transect-info.xlsx
+++ b/chl-transect-info.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\nes-ims\nes-lter-chl-transect\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jkoch\Desktop\LTER\nes-lter-chl-transect\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9DAC945-7611-42F6-973A-0E0D4F40ABAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7348600F-F59A-4A6B-A591-C5206CD28C22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1120" yWindow="1190" windowWidth="16080" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ColumnHeaders" sheetId="1" r:id="rId1"/>
@@ -334,9 +334,6 @@
     <t>OCE-1743430</t>
   </si>
   <si>
-    <t>distance</t>
-  </si>
-  <si>
     <t>Distance greater than 2 km from NES-LTER standard station</t>
   </si>
   <si>
@@ -647,6 +644,9 @@
   </si>
   <si>
     <t>Depth of sample below sea surface http://vocab.nerc.ac.uk/collection/P09/current/DEPH/</t>
+  </si>
+  <si>
+    <t>distance_km</t>
   </si>
 </sst>
 </file>
@@ -1102,14 +1102,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26.25" customWidth="1"/>
     <col min="2" max="2" width="65" customWidth="1"/>
-    <col min="5" max="5" width="20.375" customWidth="1"/>
+    <col min="5" max="5" width="20.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1132,7 +1132,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>36</v>
       </c>
@@ -1143,7 +1143,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>37</v>
       </c>
@@ -1154,7 +1154,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>38</v>
       </c>
@@ -1165,9 +1165,9 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
@@ -1179,13 +1179,13 @@
         <v>49</v>
       </c>
       <c r="F5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>42</v>
       </c>
@@ -1199,13 +1199,13 @@
         <v>50</v>
       </c>
       <c r="F6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G6" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>43</v>
       </c>
@@ -1219,18 +1219,18 @@
         <v>50</v>
       </c>
       <c r="F7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G7" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>44</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C8" t="s">
         <v>47</v>
@@ -1239,24 +1239,24 @@
         <v>51</v>
       </c>
       <c r="F8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G8" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C9" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>39</v>
       </c>
@@ -1267,23 +1267,23 @@
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>68</v>
       </c>
       <c r="B11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C11" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>40</v>
       </c>
       <c r="B12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>47</v>
@@ -1292,18 +1292,18 @@
         <v>69</v>
       </c>
       <c r="F12" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G12" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>41</v>
       </c>
       <c r="B13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>47</v>
@@ -1312,57 +1312,57 @@
         <v>69</v>
       </c>
       <c r="F13" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G13" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
+        <v>108</v>
+      </c>
+      <c r="B14" t="s">
         <v>109</v>
-      </c>
-      <c r="B14" t="s">
-        <v>110</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>79</v>
       </c>
       <c r="B15" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>71</v>
       </c>
       <c r="B16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C16" t="s">
         <v>45</v>
       </c>
       <c r="F16" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G16" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>205</v>
+      </c>
+      <c r="B17" t="s">
         <v>102</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>101</v>
-      </c>
-      <c r="B17" t="s">
-        <v>103</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>47</v>
@@ -1371,10 +1371,10 @@
         <v>70</v>
       </c>
       <c r="F17" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G17" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -1385,14 +1385,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.375" customWidth="1"/>
-    <col min="2" max="2" width="24.875" customWidth="1"/>
+    <col min="1" max="1" width="24.33203125" customWidth="1"/>
+    <col min="2" max="2" width="24.83203125" customWidth="1"/>
     <col min="3" max="3" width="21.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1403,7 +1403,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>84</v>
       </c>
@@ -1414,7 +1414,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>84</v>
       </c>
@@ -1425,7 +1425,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>84</v>
       </c>
@@ -1436,7 +1436,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>79</v>
       </c>
@@ -1447,7 +1447,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>79</v>
       </c>
@@ -1458,7 +1458,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>79</v>
       </c>
@@ -1469,147 +1469,147 @@
         <v>92</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>68</v>
       </c>
       <c r="B8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C8" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>68</v>
       </c>
       <c r="B9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C9" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>68</v>
       </c>
       <c r="B10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C10" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>68</v>
       </c>
       <c r="B11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C11" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>68</v>
       </c>
       <c r="B12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C12" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>68</v>
       </c>
       <c r="B13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C13" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>68</v>
       </c>
       <c r="B14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C14" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>68</v>
       </c>
       <c r="B15" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C15" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B17">
         <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B18">
         <v>3</v>
       </c>
       <c r="C18" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B19">
         <v>4</v>
       </c>
       <c r="C19" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B20">
         <v>9</v>
       </c>
       <c r="C20" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -1620,14 +1620,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J14"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22.25" customWidth="1"/>
-    <col min="6" max="6" width="17.375" customWidth="1"/>
+    <col min="6" max="6" width="17.33203125" customWidth="1"/>
     <col min="7" max="7" width="14.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>7</v>
       </c>
@@ -1659,7 +1659,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -1688,15 +1688,15 @@
         <v>24</v>
       </c>
       <c r="J2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C3" t="s">
         <v>25</v>
@@ -1705,10 +1705,10 @@
         <v>20</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G3" t="s">
         <v>23</v>
@@ -1720,24 +1720,24 @@
         <v>24</v>
       </c>
       <c r="J3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C4" t="s">
         <v>131</v>
-      </c>
-      <c r="C4" t="s">
-        <v>132</v>
       </c>
       <c r="D4" t="s">
         <v>20</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G4" t="s">
         <v>23</v>
@@ -1749,10 +1749,10 @@
         <v>24</v>
       </c>
       <c r="J4" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>57</v>
       </c>
@@ -1778,24 +1778,24 @@
         <v>24</v>
       </c>
       <c r="J5" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C6" t="s">
         <v>133</v>
-      </c>
-      <c r="C6" t="s">
-        <v>134</v>
       </c>
       <c r="D6" t="s">
         <v>20</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G6" t="s">
         <v>23</v>
@@ -1807,10 +1807,10 @@
         <v>24</v>
       </c>
       <c r="J6" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>61</v>
       </c>
@@ -1836,10 +1836,10 @@
         <v>24</v>
       </c>
       <c r="J7" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>55</v>
       </c>
@@ -1865,18 +1865,18 @@
         <v>24</v>
       </c>
       <c r="J8" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G9" t="s">
         <v>23</v>
@@ -1891,7 +1891,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -1911,7 +1911,7 @@
         <v>22</v>
       </c>
       <c r="G10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H10" t="s">
         <v>20</v>
@@ -1920,10 +1920,10 @@
         <v>24</v>
       </c>
       <c r="J10" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>57</v>
       </c>
@@ -1940,7 +1940,7 @@
         <v>60</v>
       </c>
       <c r="G11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H11" t="s">
         <v>20</v>
@@ -1949,10 +1949,10 @@
         <v>24</v>
       </c>
       <c r="J11" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>61</v>
       </c>
@@ -1969,7 +1969,7 @@
         <v>64</v>
       </c>
       <c r="G12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H12" t="s">
         <v>20</v>
@@ -1978,21 +1978,21 @@
         <v>24</v>
       </c>
       <c r="J12" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
+        <v>135</v>
+      </c>
+      <c r="C13" t="s">
         <v>136</v>
-      </c>
-      <c r="C13" t="s">
-        <v>137</v>
       </c>
       <c r="D13" t="s">
         <v>20</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G13" t="s">
         <v>26</v>
@@ -2004,10 +2004,10 @@
         <v>24</v>
       </c>
       <c r="J13" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -2027,7 +2027,7 @@
         <v>24</v>
       </c>
       <c r="J14" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -2053,39 +2053,39 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33916625-81B4-4982-852A-9AC43A1391EB}">
   <dimension ref="A1:D44"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="4" max="4" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="7" t="s">
         <v>36</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C1" s="7" t="s">
         <v>79</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B2" s="9">
         <v>201704</v>
       </c>
       <c r="C2" s="8" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="8" t="s">
         <v>155</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
-        <v>156</v>
       </c>
       <c r="B3" s="9">
         <v>20170902</v>
@@ -2094,12 +2094,12 @@
         <v>80</v>
       </c>
       <c r="D3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B4" s="9">
         <v>20171022</v>
@@ -2108,36 +2108,36 @@
         <v>85</v>
       </c>
       <c r="D4" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8" t="s">
         <v>85</v>
       </c>
       <c r="D5" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8" t="s">
         <v>85</v>
       </c>
       <c r="D6" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B7" s="9">
         <v>20180131</v>
@@ -2146,12 +2146,12 @@
         <v>81</v>
       </c>
       <c r="D7" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B8" s="9">
         <v>20180404</v>
@@ -2160,24 +2160,24 @@
         <v>85</v>
       </c>
       <c r="D8" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8" t="s">
         <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B10" s="9">
         <v>20180720</v>
@@ -2186,12 +2186,12 @@
         <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B11" s="9">
         <v>20181020</v>
@@ -2200,36 +2200,36 @@
         <v>85</v>
       </c>
       <c r="D11" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="8" t="s">
         <v>85</v>
       </c>
       <c r="D12" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8" t="s">
         <v>85</v>
       </c>
       <c r="D13" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B14" s="9">
         <v>20181112</v>
@@ -2238,12 +2238,12 @@
         <v>80</v>
       </c>
       <c r="D14" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B15" s="9">
         <v>20190201</v>
@@ -2252,12 +2252,12 @@
         <v>81</v>
       </c>
       <c r="D15" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B16" s="9">
         <v>20190414</v>
@@ -2266,24 +2266,24 @@
         <v>85</v>
       </c>
       <c r="D16" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8" t="s">
         <v>85</v>
       </c>
       <c r="D17" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B18" s="9">
         <v>20190819</v>
@@ -2292,12 +2292,12 @@
         <v>81</v>
       </c>
       <c r="D18" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B19" s="9">
         <v>20190920</v>
@@ -2306,12 +2306,12 @@
         <v>80</v>
       </c>
       <c r="D19" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B20" s="9">
         <v>20190925</v>
@@ -2320,24 +2320,24 @@
         <v>85</v>
       </c>
       <c r="D20" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B21" s="8"/>
       <c r="C21" s="8" t="s">
         <v>85</v>
       </c>
       <c r="D21" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B22" s="9">
         <v>20200201</v>
@@ -2346,12 +2346,12 @@
         <v>81</v>
       </c>
       <c r="D22" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B23" s="9">
         <v>20220605</v>
@@ -2360,9 +2360,9 @@
         <v>85</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B24" s="9">
         <v>20200704</v>
@@ -2371,12 +2371,12 @@
         <v>81</v>
       </c>
       <c r="D24" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B25" s="9">
         <v>20201013</v>
@@ -2385,12 +2385,12 @@
         <v>81</v>
       </c>
       <c r="D25" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B26" s="9">
         <v>20201028</v>
@@ -2399,18 +2399,18 @@
         <v>85</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B27" s="8"/>
       <c r="C27" s="8" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B28" s="9">
         <v>20210129</v>
@@ -2419,12 +2419,12 @@
         <v>81</v>
       </c>
       <c r="D28" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A29" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B29" s="9">
         <v>20210329</v>
@@ -2433,18 +2433,18 @@
         <v>85</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B30" s="8"/>
       <c r="C30" s="8" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B31" s="9">
         <v>20210716</v>
@@ -2453,12 +2453,12 @@
         <v>81</v>
       </c>
       <c r="D31" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B32" s="9">
         <v>20211026</v>
@@ -2467,32 +2467,32 @@
         <v>85</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A33" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B33" s="8"/>
       <c r="C33" s="8" t="s">
         <v>85</v>
       </c>
       <c r="D33" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A34" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B34" s="9">
         <v>20211117</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B35" s="9">
         <v>20211126</v>
@@ -2501,9 +2501,9 @@
         <v>80</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B36" s="9">
         <v>20220216</v>
@@ -2512,12 +2512,12 @@
         <v>81</v>
       </c>
       <c r="D36" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B37" s="9">
         <v>20220408</v>
@@ -2526,32 +2526,32 @@
         <v>85</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A38" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B38" s="8"/>
       <c r="C38" s="8" t="s">
         <v>85</v>
       </c>
       <c r="D38" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A39" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B39" s="9">
         <v>20220713</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A40" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B40" s="9">
         <v>20220729</v>
@@ -2560,23 +2560,23 @@
         <v>81</v>
       </c>
       <c r="D40" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B41" s="9">
         <v>20220804</v>
       </c>
       <c r="C41" s="8" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="8" t="s">
         <v>195</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="B42" s="9">
         <v>20221109</v>
@@ -2585,18 +2585,18 @@
         <v>85</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A43" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B43" s="8"/>
       <c r="C43" s="8" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A44" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B44" s="9">
         <v>20230111</v>
@@ -2614,12 +2614,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>30</v>
       </c>
@@ -2627,7 +2627,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>93</v>
       </c>
@@ -2635,7 +2635,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>67</v>
       </c>
@@ -2643,15 +2643,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>94</v>
       </c>
@@ -2659,7 +2659,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>95</v>
       </c>
@@ -2667,7 +2667,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>34</v>
       </c>
@@ -2675,7 +2675,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>96</v>
       </c>
@@ -2683,7 +2683,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>35</v>
       </c>
@@ -2691,7 +2691,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>98</v>
       </c>
@@ -2699,7 +2699,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>98</v>
       </c>

--- a/chl-transect-info.xlsx
+++ b/chl-transect-info.xlsx
@@ -5,19 +5,18 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jkoch\Desktop\LTER\nes-lter-chl-transect\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kmorkeski\Documents\nes-lter-chl-transect\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7348600F-F59A-4A6B-A591-C5206CD28C22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{666382C6-B896-475C-A51F-44598CEA3329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1120" yWindow="1190" windowWidth="16080" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-35625" yWindow="420" windowWidth="26835" windowHeight="20205" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ColumnHeaders" sheetId="1" r:id="rId1"/>
     <sheet name="CategoricalVariables" sheetId="5" r:id="rId2"/>
     <sheet name="Personnel" sheetId="2" r:id="rId3"/>
-    <sheet name="cruises" sheetId="6" r:id="rId4"/>
-    <sheet name="Keywords" sheetId="3" r:id="rId5"/>
+    <sheet name="Keywords" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="165">
   <si>
     <t>attributeName</t>
   </si>
@@ -178,9 +177,6 @@
     <t>categorical</t>
   </si>
   <si>
-    <t>YYYY-MM-DD hh:mm:ss</t>
-  </si>
-  <si>
     <t>degree</t>
   </si>
   <si>
@@ -334,9 +330,6 @@
     <t>OCE-1743430</t>
   </si>
   <si>
-    <t>Distance greater than 2 km from NES-LTER standard station</t>
-  </si>
-  <si>
     <t>Distance from sample location to nearest NES-LTER standard station</t>
   </si>
   <si>
@@ -481,159 +474,9 @@
     <t>0000-0003-0194-7282</t>
   </si>
   <si>
-    <t>"NA"</t>
-  </si>
-  <si>
     <t>&gt;20&amp;&lt;200</t>
   </si>
   <si>
-    <t>start_date</t>
-  </si>
-  <si>
-    <t>AR16</t>
-  </si>
-  <si>
-    <t>other</t>
-  </si>
-  <si>
-    <t>AR22</t>
-  </si>
-  <si>
-    <t>AR24A</t>
-  </si>
-  <si>
-    <t>AR24B</t>
-  </si>
-  <si>
-    <t>AR24C</t>
-  </si>
-  <si>
-    <t>EN608</t>
-  </si>
-  <si>
-    <t>AR28A</t>
-  </si>
-  <si>
-    <t>AR28B</t>
-  </si>
-  <si>
-    <t>EN617</t>
-  </si>
-  <si>
-    <t>AR31A</t>
-  </si>
-  <si>
-    <t>AR31B</t>
-  </si>
-  <si>
-    <t>AR31C</t>
-  </si>
-  <si>
-    <t>AR32</t>
-  </si>
-  <si>
-    <t>EN627</t>
-  </si>
-  <si>
-    <t>AR34A</t>
-  </si>
-  <si>
-    <t>AR34B</t>
-  </si>
-  <si>
-    <t>EN644</t>
-  </si>
-  <si>
-    <t>AR38</t>
-  </si>
-  <si>
-    <t>AR39A</t>
-  </si>
-  <si>
-    <t>AR39B</t>
-  </si>
-  <si>
-    <t>EN649</t>
-  </si>
-  <si>
-    <t>AR44</t>
-  </si>
-  <si>
-    <t>EN655</t>
-  </si>
-  <si>
-    <t>EN657</t>
-  </si>
-  <si>
-    <t>AR48A</t>
-  </si>
-  <si>
-    <t>AR48B</t>
-  </si>
-  <si>
-    <t>EN661</t>
-  </si>
-  <si>
-    <t>AR52A</t>
-  </si>
-  <si>
-    <t>AR52B</t>
-  </si>
-  <si>
-    <t>EN668</t>
-  </si>
-  <si>
-    <t>AR61A</t>
-  </si>
-  <si>
-    <t>AR61B</t>
-  </si>
-  <si>
-    <t>AR62</t>
-  </si>
-  <si>
-    <t>AR63</t>
-  </si>
-  <si>
-    <t>AT46</t>
-  </si>
-  <si>
-    <t>AR66A</t>
-  </si>
-  <si>
-    <t>AR66B</t>
-  </si>
-  <si>
-    <t>EN685</t>
-  </si>
-  <si>
-    <t>EN687</t>
-  </si>
-  <si>
-    <t>EN688</t>
-  </si>
-  <si>
-    <t>OTZ</t>
-  </si>
-  <si>
-    <t>AR70A</t>
-  </si>
-  <si>
-    <t>AR70B</t>
-  </si>
-  <si>
-    <t>EN695</t>
-  </si>
-  <si>
-    <t>in_version2</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>SMD</t>
-  </si>
-  <si>
     <t>Identifier for project that funded the cruise (or sample when available)</t>
   </si>
   <si>
@@ -646,14 +489,47 @@
     <t>Depth of sample below sea surface http://vocab.nerc.ac.uk/collection/P09/current/DEPH/</t>
   </si>
   <si>
-    <t>distance_km</t>
+    <t>distance</t>
+  </si>
+  <si>
+    <t>Frankie</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>Lopez</t>
+  </si>
+  <si>
+    <t>frankie.lopez@uri.edu</t>
+  </si>
+  <si>
+    <t>0009-0002-4309-2374</t>
+  </si>
+  <si>
+    <t>"NaN"</t>
+  </si>
+  <si>
+    <t>Megan</t>
+  </si>
+  <si>
+    <t>Ferguson</t>
+  </si>
+  <si>
+    <t>megan.ferguson@whoi.edu</t>
+  </si>
+  <si>
+    <t>0009-0002-4496-6600</t>
+  </si>
+  <si>
+    <t>YYYY-MM-DDThh:mm:ssZ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -687,19 +563,6 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -720,36 +583,10 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="1">
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
-      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -760,7 +597,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -772,19 +609,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1102,14 +927,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.25" customWidth="1"/>
+    <col min="1" max="1" width="26.19921875" customWidth="1"/>
     <col min="2" max="2" width="65" customWidth="1"/>
-    <col min="5" max="5" width="20.33203125" customWidth="1"/>
+    <col min="5" max="5" width="20.296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1132,249 +957,243 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>36</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>37</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>38</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
         <v>46</v>
       </c>
       <c r="E5" t="s">
-        <v>49</v>
-      </c>
-      <c r="F5" t="s">
-        <v>150</v>
-      </c>
-      <c r="G5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>42</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C6" t="s">
         <v>47</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F6" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="G6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>43</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C7" t="s">
         <v>47</v>
       </c>
       <c r="D7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F7" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="G7" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="11" t="s">
-        <v>204</v>
+      <c r="B8" s="7" t="s">
+        <v>152</v>
       </c>
       <c r="C8" t="s">
         <v>47</v>
       </c>
       <c r="D8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" t="s">
+        <v>159</v>
+      </c>
+      <c r="G8" t="s">
         <v>51</v>
       </c>
-      <c r="F8" t="s">
-        <v>150</v>
-      </c>
-      <c r="G8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B9" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C9" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B11" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C11" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>40</v>
       </c>
       <c r="B12" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F12" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="G12" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>41</v>
       </c>
       <c r="B13" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F13" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="G13" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B14" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B15" t="s">
-        <v>201</v>
+        <v>149</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B16" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C16" t="s">
         <v>45</v>
       </c>
       <c r="F16" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="G16" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>205</v>
+        <v>153</v>
       </c>
       <c r="B17" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F17" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="G17" t="s">
-        <v>101</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1385,231 +1204,231 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.33203125" customWidth="1"/>
-    <col min="2" max="2" width="24.83203125" customWidth="1"/>
-    <col min="3" max="3" width="21.75" customWidth="1"/>
+    <col min="1" max="1" width="24.296875" customWidth="1"/>
+    <col min="2" max="2" width="24.796875" customWidth="1"/>
+    <col min="3" max="3" width="21.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" t="s">
         <v>53</v>
       </c>
-      <c r="C1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7" t="s">
         <v>84</v>
       </c>
-      <c r="B2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>84</v>
-      </c>
-      <c r="B3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>84</v>
-      </c>
-      <c r="B4" t="s">
-        <v>86</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="C7" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>79</v>
-      </c>
-      <c r="B5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B7" t="s">
-        <v>85</v>
-      </c>
-      <c r="C7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C8" t="s">
         <v>110</v>
       </c>
-      <c r="C8" t="s">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B9" t="s">
+        <v>109</v>
+      </c>
+      <c r="C9" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>68</v>
-      </c>
-      <c r="B9" t="s">
-        <v>111</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="C10" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B11" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>68</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C11" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B12" t="s">
         <v>114</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C12" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>68</v>
-      </c>
-      <c r="B11" t="s">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" t="s">
         <v>115</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C13" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>68</v>
-      </c>
-      <c r="B12" t="s">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" t="s">
         <v>116</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C14" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>68</v>
-      </c>
-      <c r="B13" t="s">
-        <v>117</v>
-      </c>
-      <c r="C13" t="s">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>67</v>
+      </c>
+      <c r="B15" t="s">
+        <v>148</v>
+      </c>
+      <c r="C15" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>68</v>
-      </c>
-      <c r="B14" t="s">
-        <v>118</v>
-      </c>
-      <c r="C14" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>68</v>
-      </c>
-      <c r="B15" t="s">
-        <v>151</v>
-      </c>
-      <c r="C15" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B17">
         <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B18">
         <v>3</v>
       </c>
       <c r="C18" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B19">
         <v>4</v>
       </c>
       <c r="C19" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B20">
         <v>9</v>
       </c>
       <c r="C20" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -1619,15 +1438,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:J14"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:J16"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.25" customWidth="1"/>
-    <col min="6" max="6" width="17.33203125" customWidth="1"/>
-    <col min="7" max="7" width="14.25" customWidth="1"/>
+    <col min="1" max="1" width="22.19921875" customWidth="1"/>
+    <col min="6" max="6" width="17.296875" customWidth="1"/>
+    <col min="7" max="7" width="14.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>7</v>
       </c>
@@ -1659,7 +1478,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -1688,15 +1507,15 @@
         <v>24</v>
       </c>
       <c r="J2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C3" t="s">
         <v>25</v>
@@ -1705,10 +1524,10 @@
         <v>20</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G3" t="s">
         <v>23</v>
@@ -1720,24 +1539,24 @@
         <v>24</v>
       </c>
       <c r="J3" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D4" t="s">
         <v>20</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G4" t="s">
         <v>23</v>
@@ -1749,24 +1568,24 @@
         <v>24</v>
       </c>
       <c r="J4" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>57</v>
+        <v>160</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>161</v>
       </c>
       <c r="D5" t="s">
         <v>20</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F5" t="s">
-        <v>60</v>
+        <v>162</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>163</v>
       </c>
       <c r="G5" t="s">
         <v>23</v>
@@ -1774,28 +1593,25 @@
       <c r="H5" t="s">
         <v>20</v>
       </c>
-      <c r="I5" t="s">
-        <v>24</v>
-      </c>
       <c r="J5" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>132</v>
+        <v>56</v>
       </c>
       <c r="C6" t="s">
-        <v>133</v>
+        <v>57</v>
       </c>
       <c r="D6" t="s">
         <v>20</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>138</v>
+        <v>58</v>
       </c>
       <c r="F6" t="s">
-        <v>140</v>
+        <v>59</v>
       </c>
       <c r="G6" t="s">
         <v>23</v>
@@ -1807,24 +1623,24 @@
         <v>24</v>
       </c>
       <c r="J6" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>61</v>
+        <v>130</v>
       </c>
       <c r="C7" t="s">
-        <v>62</v>
+        <v>131</v>
       </c>
       <c r="D7" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>63</v>
+      <c r="E7" s="2" t="s">
+        <v>136</v>
       </c>
       <c r="F7" t="s">
-        <v>64</v>
+        <v>138</v>
       </c>
       <c r="G7" t="s">
         <v>23</v>
@@ -1836,24 +1652,24 @@
         <v>24</v>
       </c>
       <c r="J7" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D8" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>65</v>
+      <c r="E8" s="4" t="s">
+        <v>62</v>
       </c>
       <c r="F8" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G8" t="s">
         <v>23</v>
@@ -1865,53 +1681,59 @@
         <v>24</v>
       </c>
       <c r="J8" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>154</v>
+      </c>
+      <c r="B9" t="s">
+        <v>155</v>
+      </c>
       <c r="C9" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="D9" t="s">
-        <v>202</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>141</v>
+        <v>20</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="F9" t="s">
+        <v>158</v>
       </c>
       <c r="G9" t="s">
         <v>23</v>
       </c>
       <c r="H9" t="s">
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="I9" t="s">
         <v>24</v>
       </c>
       <c r="J9" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="D10" t="s">
         <v>20</v>
       </c>
-      <c r="E10" t="s">
-        <v>21</v>
+      <c r="E10" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="F10" t="s">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="G10" t="s">
-        <v>106</v>
+        <v>23</v>
       </c>
       <c r="H10" t="s">
         <v>20</v>
@@ -1920,56 +1742,53 @@
         <v>24</v>
       </c>
       <c r="J10" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>57</v>
-      </c>
+        <v>151</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
-        <v>58</v>
+        <v>140</v>
       </c>
       <c r="D11" t="s">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F11" t="s">
-        <v>60</v>
+        <v>139</v>
       </c>
       <c r="G11" t="s">
-        <v>106</v>
+        <v>23</v>
       </c>
       <c r="H11" t="s">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="I11" t="s">
         <v>24</v>
       </c>
       <c r="J11" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>61</v>
+        <v>17</v>
+      </c>
+      <c r="B12" t="s">
+        <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="D12" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>63</v>
+      <c r="E12" t="s">
+        <v>21</v>
       </c>
       <c r="F12" t="s">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="G12" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H12" t="s">
         <v>20</v>
@@ -1978,24 +1797,27 @@
         <v>24</v>
       </c>
       <c r="J12" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>135</v>
+        <v>56</v>
       </c>
       <c r="C13" t="s">
-        <v>136</v>
+        <v>57</v>
       </c>
       <c r="D13" t="s">
         <v>20</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>137</v>
+        <v>58</v>
+      </c>
+      <c r="F13" t="s">
+        <v>59</v>
       </c>
       <c r="G13" t="s">
-        <v>26</v>
+        <v>104</v>
       </c>
       <c r="H13" t="s">
         <v>20</v>
@@ -2004,21 +1826,27 @@
         <v>24</v>
       </c>
       <c r="J13" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>60</v>
+      </c>
+      <c r="C14" t="s">
+        <v>61</v>
       </c>
       <c r="D14" t="s">
         <v>20</v>
       </c>
-      <c r="E14" t="s">
-        <v>28</v>
+      <c r="E14" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F14" t="s">
+        <v>63</v>
       </c>
       <c r="G14" t="s">
-        <v>29</v>
+        <v>104</v>
       </c>
       <c r="H14" t="s">
         <v>20</v>
@@ -2027,22 +1855,71 @@
         <v>24</v>
       </c>
       <c r="J14" t="s">
-        <v>203</v>
+        <v>151</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>133</v>
+      </c>
+      <c r="C15" t="s">
+        <v>134</v>
+      </c>
+      <c r="D15" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="G15" t="s">
+        <v>26</v>
+      </c>
+      <c r="H15" t="s">
+        <v>20</v>
+      </c>
+      <c r="I15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J15" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" t="s">
+        <v>28</v>
+      </c>
+      <c r="G16" t="s">
+        <v>29</v>
+      </c>
+      <c r="H16" t="s">
+        <v>20</v>
+      </c>
+      <c r="I16" t="s">
+        <v>24</v>
+      </c>
+      <c r="J16" t="s">
+        <v>151</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="E11" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
-    <hyperlink ref="E12" r:id="rId2" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
-    <hyperlink ref="E7" r:id="rId3" xr:uid="{00000000-0004-0000-0200-000002000000}"/>
-    <hyperlink ref="E5" r:id="rId4" xr:uid="{00000000-0004-0000-0200-000003000000}"/>
-    <hyperlink ref="E8" r:id="rId5" xr:uid="{00000000-0004-0000-0200-000004000000}"/>
+    <hyperlink ref="E13" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
+    <hyperlink ref="E14" r:id="rId2" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
+    <hyperlink ref="E8" r:id="rId3" xr:uid="{00000000-0004-0000-0200-000002000000}"/>
+    <hyperlink ref="E6" r:id="rId4" xr:uid="{00000000-0004-0000-0200-000003000000}"/>
+    <hyperlink ref="E10" r:id="rId5" xr:uid="{00000000-0004-0000-0200-000004000000}"/>
     <hyperlink ref="E4" r:id="rId6" xr:uid="{00000000-0004-0000-0200-000006000000}"/>
-    <hyperlink ref="E13" r:id="rId7" xr:uid="{00000000-0004-0000-0200-000007000000}"/>
-    <hyperlink ref="E6" r:id="rId8" xr:uid="{00000000-0004-0000-0200-000008000000}"/>
+    <hyperlink ref="E15" r:id="rId7" xr:uid="{00000000-0004-0000-0200-000007000000}"/>
+    <hyperlink ref="E7" r:id="rId8" xr:uid="{00000000-0004-0000-0200-000008000000}"/>
     <hyperlink ref="E3" r:id="rId9" xr:uid="{00000000-0004-0000-0200-000009000000}"/>
-    <hyperlink ref="E9" r:id="rId10" xr:uid="{00000000-0004-0000-0200-00000A000000}"/>
+    <hyperlink ref="E11" r:id="rId10" xr:uid="{00000000-0004-0000-0200-00000A000000}"/>
     <hyperlink ref="E2" r:id="rId11" xr:uid="{00000000-0004-0000-0200-00000B000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2051,575 +1928,14 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33916625-81B4-4982-852A-9AC43A1391EB}">
-  <dimension ref="A1:D44"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="4" max="4" width="10.75" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="B2" s="9">
-        <v>201704</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="B3" s="9">
-        <v>20170902</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="D3" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="B4" s="9">
-        <v>20171022</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="D4" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="D5" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="D6" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="B7" s="9">
-        <v>20180131</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D7" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="B8" s="9">
-        <v>20180404</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="D8" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="D9" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="B10" s="9">
-        <v>20180720</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D10" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="B11" s="9">
-        <v>20181020</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="D11" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="D12" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="D13" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="B14" s="9">
-        <v>20181112</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="D14" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="B15" s="9">
-        <v>20190201</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D15" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="B16" s="9">
-        <v>20190414</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="D16" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="D17" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="B18" s="9">
-        <v>20190819</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D18" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="B19" s="9">
-        <v>20190920</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="D19" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="B20" s="9">
-        <v>20190925</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="D20" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="D21" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="B22" s="9">
-        <v>20200201</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D22" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="B23" s="9">
-        <v>20220605</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="B24" s="9">
-        <v>20200704</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D24" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="B25" s="9">
-        <v>20201013</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D25" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="B26" s="9">
-        <v>20201028</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="B28" s="9">
-        <v>20210129</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D28" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="B29" s="9">
-        <v>20210329</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="B31" s="9">
-        <v>20210716</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D31" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="B32" s="9">
-        <v>20211026</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="B33" s="8"/>
-      <c r="C33" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="D33" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="B34" s="9">
-        <v>20211117</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="B35" s="9">
-        <v>20211126</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="B36" s="9">
-        <v>20220216</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D36" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="B37" s="9">
-        <v>20220408</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="B38" s="8"/>
-      <c r="C38" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="D38" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="B39" s="9">
-        <v>20220713</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="B40" s="9">
-        <v>20220729</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D40" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="B41" s="9">
-        <v>20220804</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="B42" s="9">
-        <v>20221109</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="B43" s="8"/>
-      <c r="C43" s="8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="B44" s="9">
-        <v>20230111</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>30</v>
       </c>
@@ -2627,47 +1943,47 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B6" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>34</v>
       </c>
@@ -2675,15 +1991,15 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B8" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>35</v>
       </c>
@@ -2691,20 +2007,20 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B10" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B11" t="s">
         <v>98</v>
-      </c>
-      <c r="B10" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B11" t="s">
-        <v>99</v>
       </c>
     </row>
   </sheetData>
